--- a/Result/profitability/3169.xlsx
+++ b/Result/profitability/3169.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.45</v>
       </c>
       <c r="M2" t="n">
-        <v>0.8400000000000001</v>
+        <v>0.88125</v>
       </c>
       <c r="N2" t="n">
-        <v>51.78125</v>
+        <v>52.415</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.52</v>
       </c>
       <c r="M3" t="n">
-        <v>0.8225</v>
+        <v>0.8250000000000001</v>
       </c>
       <c r="N3" t="n">
-        <v>51.395</v>
+        <v>51.5675</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.54</v>
       </c>
       <c r="M4" t="n">
-        <v>0.76875</v>
+        <v>0.7512500000000001</v>
       </c>
       <c r="N4" t="n">
-        <v>50.40375</v>
+        <v>50.34375</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>0.37</v>
       </c>
       <c r="M5" t="n">
-        <v>0.67375</v>
+        <v>0.71375</v>
       </c>
       <c r="N5" t="n">
-        <v>49.32375</v>
+        <v>49.7775</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.62</v>
       </c>
       <c r="M6" t="n">
-        <v>0.6675</v>
+        <v>0.66875</v>
       </c>
       <c r="N6" t="n">
-        <v>48.51375</v>
+        <v>48.48</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>0.35</v>
       </c>
       <c r="M7" t="n">
-        <v>0.58875</v>
+        <v>0.60125</v>
       </c>
       <c r="N7" t="n">
-        <v>47.07625</v>
+        <v>47.10625</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.83</v>
       </c>
       <c r="M8" t="n">
-        <v>0.58125</v>
+        <v>0.58375</v>
       </c>
       <c r="N8" t="n">
-        <v>45.84625</v>
+        <v>45.82</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1772,7 +1772,7 @@
         <v>0.76</v>
       </c>
       <c r="M11" t="n">
-        <v>0.6512499999999999</v>
+        <v>0.65125</v>
       </c>
       <c r="N11" t="n">
         <v>45.82375</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>3169</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>253</v>
+      </c>
+      <c r="D75" t="n">
+        <v>117</v>
+      </c>
+      <c r="E75" t="n">
+        <v>137</v>
+      </c>
+      <c r="F75" t="n">
+        <v>53.99</v>
+      </c>
+      <c r="G75" t="n">
+        <v>68</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>26.66%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>7</v>
+      </c>
+      <c r="J75" t="n">
+        <v>75</v>
+      </c>
+      <c r="K75" t="n">
+        <v>62</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.9075</v>
+      </c>
+      <c r="N75" t="n">
+        <v>52.82</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.02000000000000002</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.02061855670103085</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-0.2100000000000009</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.003874538745387457</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>0.4776119402985073</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>3.630000000000003</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.07208101667990463</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
